--- a/MD/Средние.xlsx
+++ b/MD/Средние.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="17771" windowHeight="9000"/>
+    <workbookView windowWidth="17771" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1777,7 +1777,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1952,7 +1952,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2127,7 +2127,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent3"/>
+                <a:srgbClr val="00B050"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2302,7 +2302,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent4"/>
+                <a:srgbClr val="FF0000"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -2945,7 +2945,7 @@
           <c:spPr>
             <a:ln w="19050" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:srgbClr val="0070C0"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
